--- a/kinds_Write_Origin.xlsx
+++ b/kinds_Write_Origin.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mục lục" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL.md" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="230001_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="230001_2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="230002" sheetId="5" state="visible" r:id="rId5"/>
@@ -530,6 +530,8 @@
           <t>Danh sách nội dung — Write_Origin</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -654,6 +656,11 @@
           <t>SKILL.md — Write_Origin</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -661,6 +668,11 @@
           <t>TOPIK Writing Question Generator (TOPIK II)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -675,6 +687,11 @@
           <t>Khi nào dùng skill này</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -703,6 +720,11 @@
           <t>Cấu trúc thư mục</t>
         </is>
       </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -794,6 +816,11 @@
           <t>Output Format (JSON)</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -1334,6 +1361,11 @@
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
@@ -1553,6 +1585,11 @@
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="13" t="inlineStr">
@@ -1734,6 +1771,11 @@
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
@@ -1858,6 +1900,11 @@
           <t>Định dạng bài viết (writing_format)</t>
         </is>
       </c>
+      <c r="B122" s="10" t="n"/>
+      <c r="C122" s="10" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -1960,6 +2007,11 @@
           <t>Ngữ pháp đáp án (answer_grammar)</t>
         </is>
       </c>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
@@ -2076,6 +2128,11 @@
           <t>Ngữ pháp theo level (writing_grammar)</t>
         </is>
       </c>
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="10" t="n"/>
+      <c r="F138" s="10" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -2251,6 +2308,11 @@
           <t>Thang độ khó</t>
         </is>
       </c>
+      <c r="B149" s="10" t="n"/>
+      <c r="C149" s="10" t="n"/>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="10" t="n"/>
+      <c r="F149" s="10" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
@@ -2350,6 +2412,11 @@
           <t>Quy tắc chung khi gen</t>
         </is>
       </c>
+      <c r="B157" s="10" t="n"/>
+      <c r="C157" s="10" t="n"/>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="10" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
@@ -2656,6 +2723,11 @@
           <t>Kind: 230001_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2663,6 +2735,11 @@
           <t>KIND 230001_1 — Điền câu vào đoạn văn [51~52]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -2670,6 +2747,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2749,6 +2831,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2888,6 +2975,11 @@
           <t>Cấu trúc câu hỏi</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -2923,6 +3015,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -2978,6 +3075,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -3044,6 +3146,11 @@
           <t>Kind: 230001_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3051,6 +3158,11 @@
           <t>KIND 230001_2 — Điền câu vào đoạn văn [51~52]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3058,6 +3170,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -3137,6 +3254,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -3276,6 +3398,11 @@
           <t>Cấu trúc câu hỏi</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -3304,6 +3431,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -3359,6 +3491,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -3432,6 +3569,11 @@
           <t>Kind: 230002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3439,6 +3581,11 @@
           <t>KIND 230002 — Viết biểu đồ [53] [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3446,6 +3593,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -3525,6 +3677,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -3664,6 +3821,11 @@
           <t>Cấu trúc câu hỏi</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -3713,6 +3875,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -3768,6 +3935,11 @@
           <t>q_image_description</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -3782,6 +3954,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -3860,6 +4037,11 @@
           <t>Kind: 230003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3867,6 +4049,11 @@
           <t>KIND 230003 — Trình bày quan điểm cá nhân [54]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3874,6 +4061,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -3953,6 +4145,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -4092,6 +4289,11 @@
           <t>Cấu trúc câu hỏi</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -4148,6 +4350,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -4203,6 +4410,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">

--- a/kinds_Write_Origin.xlsx
+++ b/kinds_Write_Origin.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "vi": "&lt;giải thích tiếng Việt&gt;",</t>
+          <t xml:space="preserve">        "vi": "&lt;giải thích tiếng Việt — GHI RÕ trap type cho từng đáp án sai&gt;",</t>
         </is>
       </c>
     </row>
@@ -972,112 +972,105 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      },</t>
+          <t xml:space="preserve">      }</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "question_feature": "&lt;mã đặc điểm từ bảng question_feature&gt;",</t>
+          <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "difficulty": &lt;mức độ khó 1-4&gt;,</t>
+          <t xml:space="preserve">  ],</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "distractor_traps": {</t>
+          <t xml:space="preserve">  "level": 2,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "1": "&lt;trap code cho đáp án 1 — rỗng nếu là đáp án đúng&gt;",</t>
+          <t xml:space="preserve">  "kind": "230001_1",</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "2": "&lt;trap code cho đáp án 2&gt;",</t>
+          <t xml:space="preserve">  "count_question": 1,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "3": "&lt;trap code cho đáp án 3&gt;",</t>
+          <t xml:space="preserve">  "tag": "write"</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "4": "&lt;trap code cho đáp án 4&gt;"</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      }</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    }</t>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>Trường tùy chọn (OPTIONAL — chỉ thêm nếu cần phân tích chuyên sâu)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ],</t>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>Các trường sau KHÔNG bắt buộc khi gen câu hỏi. Samples.json không chứa các trường này. Chỉ thêm khi user yêu cầu phân tích metadata:</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "level": 2,</t>
+          <t>// Trong content[]:</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "kind": "230001_1",</t>
+          <t>"question_feature": "&lt;mã từ bảng question_feature&gt;",</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "count_question": 1,</t>
+          <t>"difficulty": 3,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "tag": "write",</t>
+          <t>"distractor_traps": {</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "topic": "&lt;mã chủ đề từ bảng topic&gt;"</t>
+          <t xml:space="preserve">  "1": "", "2": "trap_partial_truth", "3": "trap_grammar_connector", "4": "trap_wrong_inference"</t>
         </is>
       </c>
     </row>
@@ -1088,775 +1081,803 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>// Ở cấp top-level:</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>"topic": "daily_routine"</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Khác biệt so với Listen/Read</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>Trường</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>Listen</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>Write</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>`g_text_audio`</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Nội dung audio</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Luôn rỗng</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Luôn rỗng</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>`g_text`</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Thường rỗng</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn văn chung</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Đề bài viết (230002, 230003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>`q_text`</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Câu hỏi phụ</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn văn/câu hỏi</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Đoạn văn cần điền hoặc câu hỏi phụ</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>`tag`</t>
+          <t>`g_text_audio`</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>`"listen"`</t>
+          <t>Nội dung audio</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>`"read"`</t>
+          <t>Luôn rỗng</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>`"write"`</t>
+          <t>Luôn rỗng</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>`q_image`</t>
+          <t>`g_text`</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Rỗng</t>
+          <t>Thường rỗng</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>URL ảnh</t>
+          <t>Đoạn văn chung</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>URL ảnh đề bài (230001)</t>
+          <t>Đề bài viết (230002, 230003)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>`g_image`</t>
+          <t>`q_text`</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Rỗng</t>
+          <t>Câu hỏi phụ</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Rỗng</t>
+          <t>Đoạn văn/câu hỏi</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>URL ảnh biểu đồ (230002)</t>
+          <t>Đoạn văn cần điền hoặc câu hỏi phụ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
+          <t>`tag`</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>`"listen"`</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>`"read"`</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>`"write"`</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>`q_image`</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Rỗng</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>URL ảnh</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>URL ảnh đề bài (230001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>`g_image`</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Rỗng</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Rỗng</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>URL ảnh biểu đồ (230002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
           <t>`level`</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>1 hoặc 2</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>1 hoặc 2</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>**Chỉ level 2**</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Đặc điểm riêng của Write</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>• 230001_1, 230001_2: Câu hỏi dạng trắc nghiệm — chọn cặp (ㄱ)-(ㄴ) đúng để điền vào đoạn văn</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>• 230002: Có g_image (biểu đồ/đồ thị) + g_text (đề bài). count_question=3 (3 câu hỏi phụ về biểu đồ)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>• 230003: Có g_text (đề bài dài). count_question=10 (10 câu hỏi phụ: điền từ, chọn ngữ pháp, nội dung)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="13" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Format bổ sung cho kind có ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": {</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "image": "&lt;mô tả chi tiết nội dung hình ảnh (đoạn văn, biểu đồ)&gt;"</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  "q_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "&lt;mô tả chi tiết nội dung hình ảnh (đoạn văn, biểu đồ)&gt;"</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Áp dụng cho: 230001_1, 230001_2 (ảnh đoạn văn có chỗ trống), 230002 (ảnh biểu đồ).</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ Lưu ý: q_image_description là trường chỉ dùng khi gen câu hỏi mới — dùng để mô tả ảnh bằng text cho AI tạo ảnh sau. Trường này KHÔNG có trong samples.json (vì samples lấy từ dữ liệu thực đã có ảnh URL). Đặt ở cấp top-level của JSON (cùng cấp với title, general).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="10" t="n"/>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>Chủ đề Write (Level 2)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>Tiếng Hàn</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
+      <c r="D92" s="14" t="inlineStr">
         <is>
           <t>Kind thường gặp</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>`daily_life`</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Daily Life &amp; Routine</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>일상생활</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>230001_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>`school_education`</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>School &amp; Education</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>학교/교육</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>230001_1, 230001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>`economy_business`</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Economy &amp; Business</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>경제/산업</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>230002</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>`environment_society`</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Environment &amp; Society</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>환경/사회</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>230002, 230003</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>`science_tech`</t>
+          <t>`daily_life`</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Daily Life &amp; Routine</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>과학/기술</t>
+          <t>일상생활</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>230002, 230003</t>
+          <t>230001_1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>`culture_event`</t>
+          <t>`school_education`</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Culture &amp; Events</t>
+          <t>School &amp; Education</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>문화/행사</t>
+          <t>학교/교육</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>230002, 230003</t>
+          <t>230001_1, 230001_2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>`psychology_behavior`</t>
+          <t>`economy_business`</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Psychology &amp; Behavior</t>
+          <t>Economy &amp; Business</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>심리/행동</t>
+          <t>경제/산업</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>230003</t>
+          <t>230002</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
+          <t>`environment_society`</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Environment &amp; Society</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>환경/사회</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>230002, 230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>`science_tech`</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>과학/기술</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>230002, 230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>`culture_event`</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Culture &amp; Events</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>문화/행사</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>230002, 230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>`psychology_behavior`</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Psychology &amp; Behavior</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>심리/행동</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
           <t>`language_expression`</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Language &amp; Expression</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>언어/표현</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>230001_2, 230003</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="11" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="10" t="n"/>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
         <is>
           <t>Nhóm 1: Bẫy ngữ pháp (Grammar Traps) — chủ yếu 230001</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
+      <c r="C105" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>`trap_grammar_ending`</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Wrong Ending</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án sai dùng sai dạng kết thúc câu (e.g. -습니다 vs -세요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Sai dạng kết thúc câu (~습니다 vs ~세요)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>230001_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>`trap_grammar_connector`</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Wrong Connector</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>Dùng sai liên từ (e.g. -기 때문에 vs -어서 vs -니까)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>`trap_grammar_tense`</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Wrong Tense</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>Sai thì (quá khứ/hiện tại/tương lai)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 2: Bẫy nội dung (Content Traps) — 230002, 230003</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Dùng sai liên từ (~기 때문에 vs ~어서)</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>230001_1, 230001_2, 230003</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
+          <t>`trap_grammar_tense`</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Wrong Tense</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Sai thì (quá khứ/hiện tại/tương lai)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>230001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 2: Bẫy nội dung (Content Traps) — 230002, 230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
           <t>`trap_partial_truth`</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Partial Truth</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>Đáp án sai chứa &gt;50% nội dung đúng</t>
         </is>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>230001_1, 230001_2, 230002</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>`trap_wrong_inference`</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Wrong Inference</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Suy luận hợp lý nhưng không có trong dữ liệu</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>230001_2, 230002, 230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>`trap_number_shift`</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Number/Time Shift</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>Thay đổi số liệu biểu đồ</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>`trap_wrong_inference`</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>Wrong Inference</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>Suy luận hợp lý nhưng không có trong dữ liệu</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>`trap_overgeneralize`</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Overgeneralization</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Khái quát hóa quá mức</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>Đặc điểm câu hỏi (question_feature)</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>230002</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D115" s="14" t="inlineStr">
-        <is>
-          <t>Kind áp dụng</t>
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>`trap_comparison_flip`</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Comparison Flip</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Đảo chiều so sánh trong biểu đồ</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>230002</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>`qf_fill_blank_pair`</t>
+          <t>`trap_cause_effect_swap`</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Fill Blank Pair</t>
+          <t>Cause-Effect Swap</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Chọn cặp (ㄱ)-(ㄴ) điền vào đoạn văn</t>
+          <t>Đảo quan hệ nhân quả</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>230001_1, 230001_2</t>
+          <t>230002</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>`qf_chart_comprehension`</t>
+          <t>`trap_overgeneralize`</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Chart Comprehension</t>
+          <t>Overgeneralization</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Hiểu biểu đồ, chọn mô tả đúng</t>
+          <t>Khái quát hóa quá mức</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>230002</t>
+          <t>230002, 230003</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>`qf_fill_word`</t>
+          <t>`trap_synonym_swap`</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Fill Word</t>
+          <t>Synonym Swap</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Chọn từ/ngữ pháp điền vào câu</t>
+          <t>Thay từ đồng nghĩa/gần nghĩa nhưng sai sắc thái</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -1865,132 +1886,132 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>`qf_content_match`</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Content Match</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>Chọn nội dung khớp với đề bài</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>230002, 230003</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>Định dạng bài viết (writing_format)</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="n"/>
-      <c r="C122" s="10" t="n"/>
-      <c r="D122" s="10" t="n"/>
-      <c r="E122" s="10" t="n"/>
-      <c r="F122" s="10" t="n"/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Đặc điểm câu hỏi (question_feature)</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B123" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="C123" s="14" t="inlineStr">
-        <is>
-          <t>Đặc điểm</t>
-        </is>
-      </c>
-      <c r="D123" s="14" t="inlineStr">
-        <is>
-          <t>Kind chính</t>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>`qf_fill_blank_pair`</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Fill Blank Pair</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Chọn cặp (ㄱ)-(ㄴ) điền vào đoạn văn</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>230001_1, 230001_2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>`write_fill_pair`</t>
+          <t>`qf_chart_comprehension`</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn có 2 chỗ trống (ㄱ)-(ㄴ) cần điền</t>
+          <t>Chart Comprehension</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Đoạn văn 3-5 câu, chủ đề sinh hoạt/giáo dục, 2 chỗ trống liên quan ngữ cảnh</t>
+          <t>Hiểu biểu đồ, chọn mô tả đúng</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>230001_1, 230001_2</t>
+          <t>230002</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>`write_chart_desc`</t>
+          <t>`qf_fill_word`</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Đề bài mô tả biểu đồ/đồ thị + 3 câu hỏi phụ</t>
+          <t>Fill Word</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>g_image chứa biểu đồ, g_text mô tả yêu cầu, 3 content items hỏi về số liệu/xu hướng</t>
+          <t>Chọn từ/ngữ pháp điền vào câu</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>230002</t>
+          <t>230003</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>`write_opinion`</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Đề bài trình bày quan điểm cá nhân + 10 câu hỏi phụ</t>
+          <t>Content Match</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>g_text dài (đề bài + hướng dẫn), 10 content items: điền từ, chọn ngữ pháp, nội dung khớp</t>
+          <t>Chọn nội dung khớp với đề bài</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>230003</t>
+          <t>230002, 230003</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2025,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Ngữ pháp đáp án (answer_grammar)</t>
+          <t>Định dạng bài viết (writing_format)</t>
         </is>
       </c>
       <c r="B129" s="10" t="n"/>
@@ -2026,22 +2047,32 @@
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Kind áp dụng</t>
+          <t>Đặc điểm</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Kind chính</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>`ans_sentence_pair`</t>
+          <t>`write_fill_pair`</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Đáp án là cặp câu (ㄱ)-(ㄴ), mỗi câu 5-15 ký tự</t>
+          <t>Đoạn văn có 2 chỗ trống (ㄱ)-(ㄴ) cần điền</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Đoạn văn 3-5 câu, chủ đề sinh hoạt/giáo dục, 2 chỗ trống liên quan ngữ cảnh</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>230001_1, 230001_2</t>
         </is>
@@ -2050,15 +2081,20 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>`ans_sentence_plain`</t>
+          <t>`write_chart_desc`</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Đáp án là câu trần thuật về biểu đồ (~ㄴ다/한다)</t>
+          <t>Đề bài mô tả biểu đồ/đồ thị + 3 câu hỏi phụ</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>g_image chứa biểu đồ, g_text mô tả yêu cầu, 3 content items hỏi về số liệu/xu hướng</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>230002</t>
         </is>
@@ -2067,547 +2103,620 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>`ans_grammar_form`</t>
+          <t>`write_opinion`</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Đáp án là cấu trúc ngữ pháp (liên từ, kết thúc câu)</t>
+          <t>Đề bài trình bày quan điểm cá nhân + 10 câu hỏi phụ</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>230003 (câu điền ngữ pháp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+          <t>g_text dài (đề bài + hướng dẫn), 10 content items: điền từ, chọn ngữ pháp, nội dung khớp</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>Ngữ pháp đáp án (answer_grammar)</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n"/>
+      <c r="C136" s="10" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="10" t="n"/>
+      <c r="F136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>`ans_sentence_pair`</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là cặp câu (ㄱ)-(ㄴ), mỗi câu 5-15 ký tự</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>230001_1, 230001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>`ans_sentence_long`</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là câu dài (20+ ký tự) mô tả nội dung</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>230003 (câu nội dung)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>`ans_noun_phrase`</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là danh từ/cụm danh từ</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>230003 (câu điền từ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="9" t="inlineStr">
-        <is>
-          <t>Ngữ pháp theo level (writing_grammar)</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="n"/>
-      <c r="C138" s="10" t="n"/>
-      <c r="D138" s="10" t="n"/>
-      <c r="E138" s="10" t="n"/>
-      <c r="F138" s="10" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>Write chỉ có trong TOPIK II (Level 2) — sử dụng ngữ pháp trung-cao cấp:</t>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là câu dài (20+ ký tự) mô tả biểu đồ</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>230002</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="14" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="B140" s="14" t="inlineStr">
-        <is>
-          <t>Ngữ pháp</t>
-        </is>
-      </c>
-      <c r="C140" s="14" t="inlineStr">
-        <is>
-          <t>Ví dụ</t>
-        </is>
-      </c>
-      <c r="D140" s="14" t="inlineStr">
-        <is>
-          <t>Kind chính</t>
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>`ans_word_phrase`</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là từ/cụm từ ngắn</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>230003</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
+          <t>`ans_sentence_medium`</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là câu trung bình (10-20 ký tự)</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Ngữ pháp theo level (writing_grammar)</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="10" t="n"/>
+      <c r="F144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>Write chỉ có trong TOPIK II (Level 2) — sử dụng ngữ pháp trung-cao cấp:</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>Ngữ pháp</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>Kind chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
           <t>Liên từ (연결어미)</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>~(으)며, ~(으)ㄹ 뿐만 아니라, ~는 반면에, ~(으)므로</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>경제가 성장하는 반면에 환경은...</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>230001_2, 230003</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>Kết thúc câu (종결어미)</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>~(으)ㄴ/는 것이다, ~아/어야 한다, ~(으)ㄹ 것이다</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>노력해야 한다</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>230001_1, 230003</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>Danh từ hóa (명사형)</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>~(으)ㅁ, ~기, ~는 것</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>증가하는 것으로 나타났다</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>230002</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>So sánh/đối chiếu</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>~에 비해, ~보다, ~(으)ㄴ/는 데 비해</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>작년에 비해 증가했다</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D150" s="6" t="inlineStr">
         <is>
           <t>230002</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân-kết quả</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>~기 때문에, ~(으)므로, ~(으)ㄴ 결과</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>변화한 결과로</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>230001_2, 230003</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>Trích dẫn (인용)</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>~(이)라고 하다, ~다고 생각하다</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>~라고 주장하는 사람들이 있다</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>230003</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>Thang độ khó</t>
-        </is>
-      </c>
-      <c r="B149" s="10" t="n"/>
-      <c r="C149" s="10" t="n"/>
-      <c r="D149" s="10" t="n"/>
-      <c r="E149" s="10" t="n"/>
-      <c r="F149" s="10" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="14" t="inlineStr">
-        <is>
-          <t>Mức</t>
-        </is>
-      </c>
-      <c r="B150" s="14" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="C150" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Nguyên nhân-kết quả</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>230001_1</t>
+          <t>~기 때문에, ~(으)므로, ~(으)ㄴ 결과</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>`fill_blank_easy` — Điền câu vào đoạn văn đơn giản</t>
+          <t>변화한 결과로</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>230001_2, 230003</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
+          <t>Trích dẫn (인용)</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>~(이)라고 하다, ~다고 생각하다</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>~라고 주장하는 사람들이 있다</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>230003</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>Thang độ khó</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n"/>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="14" t="inlineStr">
+        <is>
+          <t>Mức</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>230001_1</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>`fill_blank_easy` — Điền câu vào đoạn văn đơn giản</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>230001_2</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>`fill_blank_medium` — Điền câu vào đoạn văn phức tạp hơn</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>230002</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>`chart_writing` — Phân tích biểu đồ và viết</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>230003</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
         <is>
           <t>`opinion_writing` — Trình bày quan điểm cá nhân</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc chung khi gen</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="n"/>
-      <c r="C157" s="10" t="n"/>
-      <c r="D157" s="10" t="n"/>
-      <c r="E157" s="10" t="n"/>
-      <c r="F157" s="10" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="11" t="inlineStr">
-        <is>
-          <t>1. tag = "write" — luôn luôn</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>2. level = 2 — Write chỉ có trong TOPIK II</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>3. q_correct phân bố đều 1-4 — tránh thiên lệch</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t>4. explain ghi rõ trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>5. Chủ đề đa dạng — không lặp lại chủ đề trong cùng batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>6. Ngữ pháp chính xác — đáp án đúng phải đúng ngữ pháp tiếng Hàn chuẩn</t>
-        </is>
-      </c>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc chung khi gen</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="n"/>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="10" t="n"/>
+      <c r="F163" s="10" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>7. Biểu đồ mô tả rõ — kind 230002 cần q_image_description chi tiết</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="13" t="inlineStr">
-        <is>
-          <t>Kiểm tra sau khi gen (Validation Checklist)</t>
+          <t>1. tag = "write" — luôn luôn</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>2. level = 2 — Write chỉ có trong TOPIK II</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct nằm trong 1-4</t>
+          <t>3. q_correct phân bố đều 1-4 — tránh thiên lệch</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>• [ ] 4 đáp án không trùng nhau</t>
+          <t>4. explain ghi rõ trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Đáp án đúng phải đúng ngữ pháp tiếng Hàn chuẩn</t>
+          <t>5. Chủ đề đa dạng — không lặp lại chủ đề trong cùng batch</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bẫy đúng phân bố của kind (grammar traps cho 230001, content traps cho 230002/230003)</t>
+          <t>6. Ngữ pháp chính xác — đáp án đúng phải đúng ngữ pháp tiếng Hàn chuẩn</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bản dịch (vi/en) chính xác</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] explain chứa dịch + lý do đáp án đúng + ghi chú trap type cho từng đáp án sai</t>
+          <t>7. Biểu đồ mô tả rõ — kind 230002 cần q_image_description chi tiết</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra sau khi gen (Validation Checklist)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>• [ ] count_question khớp số phần tử trong content (230001: 1, 230002: 3, 230003: 10)</t>
+          <t>• [ ] q_correct nằm trong 1-4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>• [ ] tag = "write" (KHÔNG phải "listen" hay "read")</t>
+          <t>• [ ] 4 đáp án không trùng nhau</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>• [ ] level = 2 (Write chỉ có trong TOPIK II)</t>
+          <t>• [ ] Đáp án đúng phải đúng ngữ pháp tiếng Hàn chuẩn</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct phân bố đều 1-4 trong cùng batch</t>
+          <t>• [ ] Bẫy đúng phân bố của kind (grammar traps cho 230001, content traps cho 230002/230003)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Kind 230001 → có q_image_description (ảnh đoạn văn có chỗ trống)</t>
+          <t>• [ ] Bản dịch (vi/en) chính xác</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Kind 230002 → có g_image + q_image_description (ảnh biểu đồ)</t>
+          <t>• [ ] explain chứa dịch + lý do đáp án đúng + ghi chú trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Kind 230002 → số liệu biểu đồ nhất quán giữa q_image_description và đáp án</t>
+          <t>• [ ] count_question khớp số phần tử trong content (230001: 1, 230002: 3, 230003: 10)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Kind 230003 → g_text đề bài đủ dài, rõ ràng</t>
+          <t>• [ ] tag = "write" (KHÔNG phải "listen" hay "read")</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
+          <t>• [ ] level = 2 (Write chỉ có trong TOPIK II)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] q_correct phân bố đều 1-4 trong cùng batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Kind 230001 → có q_image_description (ảnh đoạn văn có chỗ trống)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Kind 230002 → có g_image + q_image_description (ảnh biểu đồ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Kind 230002 → số liệu biểu đồ nhất quán giữa q_image_description và đáp án</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Kind 230003 → g_text đề bài đủ dài, rõ ràng</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
           <t>• [ ] Chủ đề không trùng lặp trong cùng batch</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="117">
     <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A161:F161"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
@@ -2615,84 +2724,89 @@
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A99:F99"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A149:F149"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A163:F163"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A167:F167"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A182:F182"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A162:F162"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A136:F136"/>
     <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A181:F181"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A100:F100"/>
     <mergeCell ref="A171:F171"/>
-    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A165:F165"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A173:F173"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A185:F185"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A156:F156"/>
     <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -2706,7 +2820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3065,14 +3179,14 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>`ans_pair_sentence`</t>
+          <t>`ans_sentence_pair`</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Chiến lược bẫy</t>
+          <t>Phong cách hình ảnh (từ đề thi thật)</t>
         </is>
       </c>
       <c r="B36" s="10" t="n"/>
@@ -3084,39 +3198,108 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• trap_grammar_ending: Sai dạng kết thúc câu (e.g. -ㅂ니다 vs -세요)</t>
+          <t>• Khung cửa sổ email: thanh tiêu đề xám với icon ✉ Email + nút minimize/maximize/close (□ × ở góc phải)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>• trap_grammar_connector: Dùng sai liên từ</t>
+          <t>• Header: dòng "제목: [tiêu đề email]" bên trái + ngày tháng "2025.10.10.(금)" bên phải, cùng hàng</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>• Nội dung: đoạn văn formal (합니다체), bắt đầu bằng lời chào "안녕하세요.", kết thúc lịch sự</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>• Chỗ trống: ký hiệu ㉠ ㉡ trong ngoặc đơn ( ㉠ ), font đậm, nổi bật trên dòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>• Thanh trạng thái dưới: "Internet" + biểu tượng zoom "🔍 100% ▼" ở góc phải dưới</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>• Tông màu: grayscale — thanh tiêu đề xám, nội dung trắng-đen, viền xám mỏng</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>• Font: sans-serif, nội dung cỡ vừa, tiêu đề/ngày rõ ràng</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>• trap_grammar_ending: Sai dạng kết thúc câu (e.g. -ㅂ니다 vs -세요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>• trap_grammar_connector: Dùng sai liên từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
           <t>• trap_partial_truth: Một vế đúng, một vế sai</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="22">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3129,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3481,14 +3664,14 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>`ans_pair_sentence`</t>
+          <t>`ans_sentence_pair`</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Chiến lược bẫy</t>
+          <t>Phong cách hình ảnh (từ đề thi thật)</t>
         </is>
       </c>
       <c r="B35" s="10" t="n"/>
@@ -3500,46 +3683,107 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>• trap_grammar_connector: Sai liên từ trong ngữ cảnh học thuật</t>
+          <t>• Khung văn bản thuần: không có khung email hay cửa sổ — chỉ là đoạn văn trên nền trắng, viền xám mỏng bao quanh</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• trap_grammar_tense: Sai thì/dạng động từ</t>
+          <t>• Nội dung: đoạn văn học thuật/khoa học/xã hội dài hơn 230001_1, văn phong formal (합니다체 hoặc 다체), lập luận logic chặt chẽ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>• trap_wrong_inference: Suy luận sai từ ngữ cảnh</t>
+          <t>• Chỗ trống: ký hiệu ㉠ ㉡ trong ngoặc đơn ( ㉠ ), font đậm, nổi bật trên dòng</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>• Bố cục: đoạn văn liền mạch, không có header/tiêu đề/ngày tháng — chỉ nội dung thuần túy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>• Tông màu: grayscale — nội dung trắng-đen, viền xám mỏng</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>• Font: sans-serif, cỡ vừa, dễ đọc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>• trap_grammar_connector: Sai liên từ trong ngữ cảnh học thuật</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>• trap_grammar_tense: Sai thì/dạng động từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>• trap_wrong_inference: Suy luận sai từ ngữ cảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>• trap_partial_truth: Một vế đúng, một vế sai</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="21">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3552,7 +3796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3932,7 +4176,7 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>q_image_description</t>
+          <t>Phong cách hình ảnh (từ đề thi thật)</t>
         </is>
       </c>
       <c r="B38" s="10" t="n"/>
@@ -3944,70 +4188,355 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>Mô tả chi tiết biểu đồ: loại biểu đồ (cột, đường, tròn), trục X/Y, đơn vị, xu hướng tăng/giảm, số liệu cụ thể.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Chiến lược bẫy</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
+          <t>• Bố cục infographic: chia thành 2-3 khu vực — biểu đồ tăng trưởng (trái) + bảng xếp hạng (phải) + phân tích (dưới)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>• Biểu đồ tăng trưởng: mũi tên lớn hướng lên (↗), kèm số liệu cụ thể (약 2배), nhãn năm ở trục dưới</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>• trap_number_shift: Thay đổi số liệu biểu đồ</t>
+          <t>• Bảng xếp hạng: tiêu đề đậm + bảng 2 cột (순위) so sánh 2 thời kỳ, viền kẻ mỏng</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>• trap_wrong_inference: Suy luận sai từ dữ liệu</t>
+          <t>• Phân tích/nguyên nhân: bullet points (•) với mũi tên (⇒) nối nguyên nhân → kết quả</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>• trap_overgeneralize: Khái quát hóa quá mức từ biểu đồ</t>
+          <t>• Icon minh họa: hình vẽ nhỏ đơn giản liên quan đến chủ đề (lều camping, xe hơi, v.v.) — grayscale</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
+          <t>• Tiêu đề tổng: phía trên cùng, gồm tên tổ chức khảo sát + tiêu đề nội dung, chữ đậm</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>• Tông màu: grayscale hoàn toàn — nền trắng, viền đen/xám, text đen</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>• Phong cách: compact, kiểu báo chí/infographic, nhiều thông tin trong diện tích nhỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>q_image_description — Template BẮT BUỘC</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Mô tả chi tiết biểu đồ theo format sau. Agent PHẢI viết đủ các mục:</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Loại biểu đồ: [막대 그래프 / 선 그래프 / 원 그래프 / 복합 인포그래픽]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Tiêu đề: [tiêu đề biểu đồ bằng tiếng Hàn]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Nguồn khảo sát: [tên tổ chức, năm khảo sát]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Trục X: [nhãn — ví dụ: 연도 (2018, 2019, 2020, 2021, 2022)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Trục Y: [nhãn + đơn vị — ví dụ: 참가자 수 (만 명)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Dữ liệu:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - [항목1]: [năm1: giá trị, năm2: giá trị, ...]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - [항목2]: [năm1: giá trị, năm2: giá trị, ...]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Xu hướng: [tóm tắt 1 câu — ví dụ: 전체적으로 증가 추세이며, 항목1이 가장 큰 비중을 차지함]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật: [điểm khác biệt đáng chú ý — ví dụ: 2020년에 감소 후 2021년 급격히 회복]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Ví dụ hoàn chỉnh:</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Loại biểu đồ: 막대 그래프 + 순위표</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Tiêu đề: 국내 외국인 유학생 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Nguồn khảo sát: 교육부, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Trục X: 연도 (2019, 2020, 2021, 2022, 2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Trục Y: 유학생 수 (만 명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Dữ liệu:</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 전체: 2019: 16.0, 2020: 15.3, 2021: 15.2, 2022: 16.7, 2023: 18.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 학위과정: 2019: 8.6, 2020: 8.8, 2021: 9.3, 2022: 10.5, 2023: 12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 비학위과정: 2019: 7.4, 2020: 6.5, 2021: 5.9, 2022: 6.2, 2023: 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>순위표: 출신국 TOP5 — 1위 중국(44%), 2위 베트남(23%), 3위 우즈베키스탄(6%), 4위 몽골(4%), 5위 일본(3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>Xu hướng: 코로나19로 2020-2021 감소 후 2022년부터 회복세, 학위과정 비중 지속 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật: 학위과정이 비학위과정을 역전(2021년 이후), 중국 비중 감소 추세</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Lưu ý: Số liệu trong q_image_description PHẢI nhất quán với đáp án đúng trong content[]. Nếu biểu đồ nói 18.1만 명 thì đáp án không được nói 17만 명.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>• trap_number_shift: Thay đổi số liệu biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>• trap_wrong_inference: Suy luận sai từ dữ liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>• trap_overgeneralize: Khái quát hóa quá mức từ biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
           <t>• trap_partial_truth: Mô tả đúng xu hướng nhưng sai số liệu</t>
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>• trap_comparison_flip: Đảo chiều so sánh trong biểu đồ: "A가 B보다 높다" → "B가 A보다 높다"</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>• trap_cause_effect_swap: Đảo nhân quả khi mô tả xu hướng dữ liệu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="54">
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A76:F76"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
